--- a/docs/tests for rcon2mc.xlsx
+++ b/docs/tests for rcon2mc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Desktop/repo/rcon2mc/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5B7B7F57-4C43-454C-BF98-5219FFA9D092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8EA16D-D7DA-374E-AFEA-10D755436D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27380" windowHeight="16900" xr2:uid="{7448B796-0E8F-9D43-8E37-4E4E55AED4EE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="64">
   <si>
     <t>Command Tests of rcon2mc</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,6 +278,14 @@
   </si>
   <si>
     <t>TBD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">t </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -285,7 +293,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -306,6 +314,15 @@
       <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -403,7 +420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -412,15 +429,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -442,6 +450,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,64 +805,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -855,10 +875,10 @@
       <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>26.1</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -893,10 +913,10 @@
       <c r="F5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -920,21 +940,21 @@
         <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -951,7 +971,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -969,10 +989,10 @@
       <c r="F7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1007,10 +1027,10 @@
       <c r="F8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1045,10 +1065,10 @@
       <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="G9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1072,21 +1092,21 @@
         <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1110,21 +1130,21 @@
         <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1159,10 +1179,10 @@
       <c r="F12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1197,10 +1217,10 @@
       <c r="F13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>61</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1235,10 +1255,10 @@
       <c r="F14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1262,21 +1282,21 @@
         <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1300,21 +1320,21 @@
         <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>56</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1349,10 +1369,10 @@
       <c r="F17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="7" t="s">
+      <c r="G17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1387,10 +1407,10 @@
       <c r="F18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1425,10 +1445,10 @@
       <c r="F19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="7" t="s">
+      <c r="G19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -1452,21 +1472,21 @@
         <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -1490,21 +1510,21 @@
         <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -1539,10 +1559,10 @@
       <c r="F22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="G22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -1566,21 +1586,21 @@
         <v>38</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>61</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -1615,10 +1635,10 @@
       <c r="F24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="7" t="s">
+      <c r="G24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -1653,10 +1673,10 @@
       <c r="F25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H25" s="7" t="s">
+      <c r="G25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>56</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -1691,10 +1711,10 @@
       <c r="F26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="8" t="s">
+      <c r="G26" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>56</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -1729,16 +1749,16 @@
       <c r="F27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H27" s="10" t="s">
+      <c r="G27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="8" t="s">
         <v>59</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -1767,10 +1787,10 @@
       <c r="F28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" s="8" t="s">
+      <c r="G28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>56</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -1805,10 +1825,10 @@
       <c r="F29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H29" s="7" t="s">
+      <c r="G29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -1831,22 +1851,22 @@
       <c r="B30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="7" t="s">
+      <c r="C30" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -1881,10 +1901,10 @@
       <c r="F31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H31" s="7" t="s">
+      <c r="G31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -1919,10 +1939,10 @@
       <c r="F32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H32" s="7" t="s">
+      <c r="G32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I32" s="1" t="s">

--- a/docs/tests for rcon2mc.xlsx
+++ b/docs/tests for rcon2mc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Desktop/repo/rcon2mc/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8EA16D-D7DA-374E-AFEA-10D755436D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DA8641-DD6F-974A-A5A3-BCA7EA72A16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27380" windowHeight="16900" xr2:uid="{7448B796-0E8F-9D43-8E37-4E4E55AED4EE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="62">
   <si>
     <t>Command Tests of rcon2mc</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,14 +278,6 @@
   </si>
   <si>
     <t>TBD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">t </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -451,6 +443,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -459,9 +454,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -805,64 +797,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -940,19 +932,19 @@
         <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>38</v>
@@ -971,7 +963,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">

--- a/docs/tests for rcon2mc.xlsx
+++ b/docs/tests for rcon2mc.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Desktop/repo/rcon2mc/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DA8641-DD6F-974A-A5A3-BCA7EA72A16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F92C5C-166E-FB4A-90D3-BC9D35F3B077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27380" windowHeight="16900" xr2:uid="{7448B796-0E8F-9D43-8E37-4E4E55AED4EE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="62">
   <si>
     <t>Command Tests of rcon2mc</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -327,7 +327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -351,13 +351,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -369,41 +369,13 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -412,7 +384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -422,37 +394,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -788,73 +745,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08812FD9-389F-0C48-A765-ABB757260629}">
-  <dimension ref="A1:L32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5A86ED-2E2E-3A4E-8956-0C806D168340}">
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -867,26 +805,11 @@
       <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="1">
         <v>26.1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4" s="1">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -905,26 +828,11 @@
       <c r="F5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="G5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -946,24 +854,9 @@
       <c r="G6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="10" t="s">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -981,26 +874,11 @@
       <c r="F7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1019,26 +897,11 @@
       <c r="F8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="G8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1057,26 +920,11 @@
       <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="G9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -1098,23 +946,8 @@
       <c r="G10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -1136,23 +969,8 @@
       <c r="G11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -1171,26 +989,11 @@
       <c r="F12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="G12" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -1209,26 +1012,11 @@
       <c r="F13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="G13" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1247,26 +1035,11 @@
       <c r="F14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="G14" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -1288,23 +1061,8 @@
       <c r="G15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -1323,26 +1081,11 @@
       <c r="F16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="G16" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1361,26 +1104,11 @@
       <c r="F17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="G17" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -1399,26 +1127,11 @@
       <c r="F18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="G18" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1437,26 +1150,11 @@
       <c r="F19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="G19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
@@ -1478,23 +1176,8 @@
       <c r="G20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1516,23 +1199,8 @@
       <c r="G21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
@@ -1551,26 +1219,11 @@
       <c r="F22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="G22" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -1589,26 +1242,11 @@
       <c r="F23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="G23" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
@@ -1627,26 +1265,11 @@
       <c r="F24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="G24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
@@ -1665,26 +1288,11 @@
       <c r="F25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="G25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
@@ -1703,26 +1311,11 @@
       <c r="F26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="G26" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
@@ -1741,26 +1334,11 @@
       <c r="F27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="G27" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
@@ -1779,26 +1357,11 @@
       <c r="F28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="G28" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
@@ -1817,64 +1380,34 @@
       <c r="F29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="G29" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="C30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
@@ -1893,72 +1426,733 @@
       <c r="F31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="2" t="s">
+      <c r="G31" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17" thickBot="1">
+      <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L32" s="1" t="s">
+      <c r="C32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17" thickTop="1">
+      <c r="A33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="H2:L2"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tests for rcon2mc.xlsx
+++ b/docs/tests for rcon2mc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Desktop/repo/rcon2mc/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F92C5C-166E-FB4A-90D3-BC9D35F3B077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B88F5E-4ED9-1D42-959B-A177D241DB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27380" windowHeight="16900" xr2:uid="{7448B796-0E8F-9D43-8E37-4E4E55AED4EE}"/>
   </bookViews>
@@ -38,10 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="62">
   <si>
-    <t>Command Tests of rcon2mc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>command</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -263,14 +259,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tests "NotFoundError"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tests "Success"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -278,6 +266,18 @@
   </si>
   <si>
     <t>TBD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test cases for none-player server</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test cases for players-online server</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test cases for built-in command</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -755,7 +755,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -766,13 +766,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -783,7 +783,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -794,16 +794,16 @@
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="G4" s="1">
         <v>26.1</v>
@@ -811,657 +811,657 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" thickBot="1">
       <c r="A32" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" thickTop="1">
       <c r="A33" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>2</v>
-      </c>
       <c r="C33" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -1472,7 +1472,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -1483,16 +1483,16 @@
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="G35" s="1">
         <v>26.1</v>
@@ -1500,659 +1500,659 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
